--- a/Graphene.xlsx
+++ b/Graphene.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usser\OneDrive\Рабочий стол\Проекты\Graphene Clusterization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usser\OneDrive\Рабочий стол\Projects\Graphene Clusterization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE80B21C-2570-433D-95E0-9E182B8A3A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA56926-164A-46F6-91F6-757AC8C73B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{458DB10C-8770-4CC4-BCB7-7786A49F9306}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="181">
   <si>
     <t>23-30/01/25</t>
   </si>
@@ -935,6 +935,36 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>DN</t>
+  </si>
+  <si>
+    <t>α</t>
+  </si>
+  <si>
+    <t>β</t>
+  </si>
+  <si>
+    <t>π*</t>
+  </si>
+  <si>
+    <t>Molar Masses, g/mol</t>
+  </si>
+  <si>
+    <t>Sorption, g/g</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1334,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1466,6 +1496,21 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1478,22 +1523,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5236,53 +5269,53 @@
     <col min="13" max="13" width="16.1640625" style="40" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.25" style="40" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.75" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.4140625" style="40" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="19" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="36" customFormat="1">
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="68" t="s">
         <v>129</v>
       </c>
       <c r="D1" s="53"/>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69" t="s">
+      <c r="F1" s="68"/>
+      <c r="G1" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="69" t="s">
+      <c r="I1" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69" t="s">
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="69" t="s">
+      <c r="M1" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="N1" s="69" t="s">
+      <c r="N1" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="O1" s="69" t="s">
+      <c r="O1" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="P1" s="73" t="s">
+      <c r="P1" s="66" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="37" customFormat="1" ht="18.5" thickBot="1">
       <c r="A2" s="39"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="70"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="48"/>
       <c r="E2" s="48" t="s">
         <v>117</v>
@@ -5290,8 +5323,8 @@
       <c r="F2" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
       <c r="I2" s="48" t="s">
         <v>58</v>
       </c>
@@ -5301,17 +5334,17 @@
       <c r="K2" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="74"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="67"/>
     </row>
     <row r="3" spans="1:16" s="38" customFormat="1">
       <c r="A3" s="38">
         <v>1</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="70" t="s">
         <v>137</v>
       </c>
       <c r="C3" s="53" t="s">
@@ -5354,7 +5387,7 @@
       <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B4" s="66"/>
+      <c r="B4" s="71"/>
       <c r="C4" s="41" t="s">
         <v>141</v>
       </c>
@@ -5399,7 +5432,7 @@
       <c r="A5" s="38">
         <v>3</v>
       </c>
-      <c r="B5" s="66"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="41" t="s">
         <v>8</v>
       </c>
@@ -5444,7 +5477,7 @@
       <c r="A6" s="38">
         <v>4</v>
       </c>
-      <c r="B6" s="66"/>
+      <c r="B6" s="71"/>
       <c r="C6" s="41" t="s">
         <v>142</v>
       </c>
@@ -5485,7 +5518,7 @@
       <c r="A7" s="38">
         <v>5</v>
       </c>
-      <c r="B7" s="66"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="41" t="s">
         <v>23</v>
       </c>
@@ -5526,7 +5559,7 @@
       <c r="A8" s="38">
         <v>6</v>
       </c>
-      <c r="B8" s="66"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="41" t="s">
         <v>25</v>
       </c>
@@ -5569,7 +5602,7 @@
       <c r="A9" s="38">
         <v>7</v>
       </c>
-      <c r="B9" s="66"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="41" t="s">
         <v>26</v>
       </c>
@@ -5612,7 +5645,7 @@
       <c r="A10" s="38">
         <v>8</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="48" t="s">
         <v>28</v>
       </c>
@@ -5653,7 +5686,7 @@
       <c r="A11" s="38">
         <v>9</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="70" t="s">
         <v>138</v>
       </c>
       <c r="C11" s="53" t="s">
@@ -5696,7 +5729,7 @@
       <c r="A12" s="38">
         <v>10</v>
       </c>
-      <c r="B12" s="66"/>
+      <c r="B12" s="71"/>
       <c r="C12" s="41" t="s">
         <v>145</v>
       </c>
@@ -5729,7 +5762,7 @@
       <c r="A13" s="38">
         <v>11</v>
       </c>
-      <c r="B13" s="66"/>
+      <c r="B13" s="71"/>
       <c r="C13" s="41" t="s">
         <v>146</v>
       </c>
@@ -5772,7 +5805,7 @@
       <c r="A14" s="38">
         <v>12</v>
       </c>
-      <c r="B14" s="66"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="41" t="s">
         <v>52</v>
       </c>
@@ -5817,7 +5850,7 @@
       <c r="A15" s="38">
         <v>13</v>
       </c>
-      <c r="B15" s="66"/>
+      <c r="B15" s="71"/>
       <c r="C15" s="41" t="s">
         <v>51</v>
       </c>
@@ -5862,7 +5895,7 @@
       <c r="A16" s="38">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
+      <c r="B16" s="71"/>
       <c r="C16" s="41" t="s">
         <v>61</v>
       </c>
@@ -5907,7 +5940,7 @@
       <c r="A17" s="38">
         <v>15</v>
       </c>
-      <c r="B17" s="66"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="41" t="s">
         <v>61</v>
       </c>
@@ -5952,7 +5985,7 @@
       <c r="A18" s="38">
         <v>16</v>
       </c>
-      <c r="B18" s="66"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="41" t="s">
         <v>48</v>
       </c>
@@ -5997,7 +6030,7 @@
       <c r="A19" s="38">
         <v>17</v>
       </c>
-      <c r="B19" s="66"/>
+      <c r="B19" s="71"/>
       <c r="C19" s="41" t="s">
         <v>39</v>
       </c>
@@ -6042,7 +6075,7 @@
       <c r="A20" s="38">
         <v>18</v>
       </c>
-      <c r="B20" s="66"/>
+      <c r="B20" s="71"/>
       <c r="C20" s="41" t="s">
         <v>46</v>
       </c>
@@ -6083,7 +6116,7 @@
       <c r="A21" s="38">
         <v>19</v>
       </c>
-      <c r="B21" s="66"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="41" t="s">
         <v>41</v>
       </c>
@@ -6124,7 +6157,7 @@
       <c r="A22" s="38">
         <v>20</v>
       </c>
-      <c r="B22" s="66"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="41" t="s">
         <v>139</v>
       </c>
@@ -6159,7 +6192,7 @@
       <c r="A23" s="38">
         <v>21</v>
       </c>
-      <c r="B23" s="66"/>
+      <c r="B23" s="71"/>
       <c r="C23" s="41" t="s">
         <v>110</v>
       </c>
@@ -6196,7 +6229,7 @@
       <c r="A24" s="38">
         <v>22</v>
       </c>
-      <c r="B24" s="66"/>
+      <c r="B24" s="71"/>
       <c r="C24" s="41" t="s">
         <v>85</v>
       </c>
@@ -6233,7 +6266,7 @@
       <c r="A25" s="38">
         <v>23</v>
       </c>
-      <c r="B25" s="66"/>
+      <c r="B25" s="71"/>
       <c r="C25" s="41" t="s">
         <v>85</v>
       </c>
@@ -6270,7 +6303,7 @@
       <c r="A26" s="38">
         <v>24</v>
       </c>
-      <c r="B26" s="66"/>
+      <c r="B26" s="71"/>
       <c r="C26" s="41" t="s">
         <v>144</v>
       </c>
@@ -6303,7 +6336,7 @@
       <c r="A27" s="38">
         <v>25</v>
       </c>
-      <c r="B27" s="66"/>
+      <c r="B27" s="71"/>
       <c r="C27" s="41" t="s">
         <v>47</v>
       </c>
@@ -6346,7 +6379,7 @@
       <c r="A28" s="38">
         <v>26</v>
       </c>
-      <c r="B28" s="66"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="41" t="s">
         <v>34</v>
       </c>
@@ -6387,7 +6420,7 @@
       <c r="A29" s="38">
         <v>27</v>
       </c>
-      <c r="B29" s="66"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="41" t="s">
         <v>35</v>
       </c>
@@ -6428,7 +6461,7 @@
       <c r="A30" s="38">
         <v>28</v>
       </c>
-      <c r="B30" s="66"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="41" t="s">
         <v>45</v>
       </c>
@@ -6471,7 +6504,7 @@
       <c r="A31" s="38">
         <v>29</v>
       </c>
-      <c r="B31" s="66"/>
+      <c r="B31" s="71"/>
       <c r="C31" s="41" t="s">
         <v>31</v>
       </c>
@@ -6516,7 +6549,7 @@
       <c r="A32" s="38">
         <v>30</v>
       </c>
-      <c r="B32" s="66"/>
+      <c r="B32" s="71"/>
       <c r="C32" s="41" t="s">
         <v>87</v>
       </c>
@@ -6553,7 +6586,7 @@
       <c r="A33" s="38">
         <v>31</v>
       </c>
-      <c r="B33" s="66"/>
+      <c r="B33" s="71"/>
       <c r="C33" s="41" t="s">
         <v>111</v>
       </c>
@@ -6590,7 +6623,7 @@
       <c r="A34" s="38">
         <v>32</v>
       </c>
-      <c r="B34" s="66"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="41" t="s">
         <v>65</v>
       </c>
@@ -6635,7 +6668,7 @@
       <c r="A35" s="38">
         <v>33</v>
       </c>
-      <c r="B35" s="66"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="41" t="s">
         <v>109</v>
       </c>
@@ -6670,7 +6703,7 @@
       <c r="A36" s="38">
         <v>34</v>
       </c>
-      <c r="B36" s="66"/>
+      <c r="B36" s="71"/>
       <c r="C36" s="41" t="s">
         <v>42</v>
       </c>
@@ -6715,7 +6748,7 @@
       <c r="A37" s="38">
         <v>35</v>
       </c>
-      <c r="B37" s="66"/>
+      <c r="B37" s="71"/>
       <c r="C37" s="41" t="s">
         <v>42</v>
       </c>
@@ -6760,7 +6793,7 @@
       <c r="A38" s="38">
         <v>36</v>
       </c>
-      <c r="B38" s="66"/>
+      <c r="B38" s="71"/>
       <c r="C38" s="41" t="s">
         <v>108</v>
       </c>
@@ -6795,7 +6828,7 @@
       <c r="A39" s="38">
         <v>37</v>
       </c>
-      <c r="B39" s="66"/>
+      <c r="B39" s="71"/>
       <c r="C39" s="41" t="s">
         <v>40</v>
       </c>
@@ -6838,7 +6871,7 @@
       <c r="A40" s="38">
         <v>38</v>
       </c>
-      <c r="B40" s="66"/>
+      <c r="B40" s="71"/>
       <c r="C40" s="41" t="s">
         <v>53</v>
       </c>
@@ -6883,7 +6916,7 @@
       <c r="A41" s="38">
         <v>39</v>
       </c>
-      <c r="B41" s="66"/>
+      <c r="B41" s="71"/>
       <c r="C41" s="41" t="s">
         <v>86</v>
       </c>
@@ -6916,7 +6949,7 @@
       <c r="A42" s="38">
         <v>40</v>
       </c>
-      <c r="B42" s="66"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="41" t="s">
         <v>86</v>
       </c>
@@ -6949,7 +6982,7 @@
       <c r="A43" s="38">
         <v>41</v>
       </c>
-      <c r="B43" s="67"/>
+      <c r="B43" s="72"/>
       <c r="C43" s="41" t="s">
         <v>85</v>
       </c>
@@ -6986,7 +7019,7 @@
       <c r="A44" s="38">
         <v>42</v>
       </c>
-      <c r="B44" s="67"/>
+      <c r="B44" s="72"/>
       <c r="C44" s="59" t="s">
         <v>143</v>
       </c>
@@ -7031,7 +7064,7 @@
       <c r="A45" s="38">
         <v>43</v>
       </c>
-      <c r="B45" s="68"/>
+      <c r="B45" s="73"/>
       <c r="C45" s="48" t="s">
         <v>55</v>
       </c>
@@ -7406,6 +7439,11 @@
     <sortCondition ref="C3:C10"/>
   </sortState>
   <mergeCells count="13">
+    <mergeCell ref="B11:B45"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="I1:K1"/>
@@ -7414,11 +7452,6 @@
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="B11:B45"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F52">
     <cfRule type="colorScale" priority="1">
@@ -12900,11 +12933,11 @@
       <c r="D1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
       <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
@@ -13711,14 +13744,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7506A49B-E0E1-4E26-85F9-EB1CD4D89B1C}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9" ht="14.5" thickBot="1">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -13728,8 +13762,26 @@
       <c r="C1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.5">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -13739,8 +13791,27 @@
       <c r="C2" s="64">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="55">
+        <v>0</v>
+      </c>
+      <c r="E2" s="55">
+        <v>0.373</v>
+      </c>
+      <c r="F2" s="55">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G2" s="64">
+        <v>14.3</v>
+      </c>
+      <c r="H2" s="64">
+        <v>88.105999999999995</v>
+      </c>
+      <c r="I2">
+        <f>(B2*H2)/1000</f>
+        <v>0.47502464466888317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.5">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -13750,8 +13821,27 @@
       <c r="C3" s="64">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="43">
+        <v>0</v>
+      </c>
+      <c r="E3" s="43">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="F3" s="43">
+        <v>0.71</v>
+      </c>
+      <c r="G3" s="65">
+        <v>10.5</v>
+      </c>
+      <c r="H3" s="64">
+        <v>102.089</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I44" si="0">(B3*H3)/1000</f>
+        <v>0.24227404959916313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.5">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -13761,8 +13851,27 @@
       <c r="C4" s="64">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="43">
+        <v>1.121</v>
+      </c>
+      <c r="E4" s="43">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="F4" s="43">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G4" s="65">
+        <v>20</v>
+      </c>
+      <c r="H4" s="64">
+        <v>60.052</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>0.21335807050089178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.5">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -13772,8 +13881,27 @@
       <c r="C5" s="64">
         <v>9.25</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="43">
+        <v>0</v>
+      </c>
+      <c r="E5" s="43">
+        <v>0</v>
+      </c>
+      <c r="F5" s="43">
+        <v>0</v>
+      </c>
+      <c r="G5" s="65">
+        <v>0.4</v>
+      </c>
+      <c r="H5" s="63">
+        <v>118.959</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>7.6628428277247085E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.5">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -13783,8 +13911,24 @@
       <c r="C6" s="64">
         <v>23.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="43">
+        <v>0.11</v>
+      </c>
+      <c r="E6" s="43">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F6" s="43">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="63">
+        <v>100.117</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>5.813953488358543E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.5">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -13794,8 +13938,27 @@
       <c r="C7" s="64">
         <v>3.09</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="43">
+        <v>0</v>
+      </c>
+      <c r="E7" s="43">
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="43">
+        <v>0.69</v>
+      </c>
+      <c r="G7" s="65">
+        <v>23.7</v>
+      </c>
+      <c r="H7" s="63">
+        <v>266.31799999999998</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>2.4298882940355589E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.5">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -13805,8 +13968,24 @@
       <c r="C8" s="64">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="43">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E8" s="43">
+        <v>0.6</v>
+      </c>
+      <c r="F8" s="43">
+        <v>0.75</v>
+      </c>
+      <c r="H8" s="64">
+        <v>96.084999999999994</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0.14143485173878864</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" thickBot="1">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -13816,8 +13995,18 @@
       <c r="C9" s="64">
         <v>40.299999999999997</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="H9" s="64">
+        <v>112.084</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>6.0954556269324729E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.5">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -13827,8 +14016,24 @@
       <c r="C10" s="64">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="55">
+        <v>0</v>
+      </c>
+      <c r="E10" s="55">
+        <v>0.373</v>
+      </c>
+      <c r="F10" s="55">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H10" s="64">
+        <v>88.105999999999995</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>0.36658952748594059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.5">
       <c r="A11" t="s">
         <v>148</v>
       </c>
@@ -13838,8 +14043,18 @@
       <c r="C11" s="64">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="H11" s="64">
+        <v>44.070999999999998</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>0.24214967198458301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17.5">
       <c r="A12" t="s">
         <v>149</v>
       </c>
@@ -13849,8 +14064,27 @@
       <c r="C12" s="64">
         <v>21.01</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="43">
+        <v>0.19</v>
+      </c>
+      <c r="E12" s="43">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="43">
+        <v>0.75</v>
+      </c>
+      <c r="G12" s="65">
+        <v>14.1</v>
+      </c>
+      <c r="H12" s="64">
+        <v>41.052999999999997</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>0.16007532956688336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.5">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -13860,8 +14094,27 @@
       <c r="C13" s="64">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="43">
+        <v>0</v>
+      </c>
+      <c r="E13" s="43">
+        <v>0.69</v>
+      </c>
+      <c r="F13" s="43">
+        <v>1.18</v>
+      </c>
+      <c r="G13" s="65">
+        <v>26.6</v>
+      </c>
+      <c r="H13" s="64">
+        <v>73.094999999999999</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>0.37953260296433916</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17.5">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -13871,8 +14124,27 @@
       <c r="C14" s="64">
         <v>46.68</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="43">
+        <v>0</v>
+      </c>
+      <c r="E14" s="43">
+        <v>0.69</v>
+      </c>
+      <c r="F14" s="43">
+        <v>1</v>
+      </c>
+      <c r="G14" s="65">
+        <v>29.8</v>
+      </c>
+      <c r="H14" s="64">
+        <v>78.129000000000005</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.46242182696840956</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17.5">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -13882,8 +14154,27 @@
       <c r="C15" s="64">
         <v>2.42</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="43">
+        <v>0</v>
+      </c>
+      <c r="E15" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="F15" s="43">
+        <v>0.37</v>
+      </c>
+      <c r="G15" s="65">
+        <v>61</v>
+      </c>
+      <c r="H15" s="64">
+        <v>101.193</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>0.20038563985377666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.5">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -13893,8 +14184,27 @@
       <c r="C16" s="64">
         <v>2.42</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="43">
+        <v>0</v>
+      </c>
+      <c r="E16" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="43">
+        <v>0.37</v>
+      </c>
+      <c r="G16" s="65">
+        <v>61</v>
+      </c>
+      <c r="H16" s="64">
+        <v>101.193</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>0.1039236225960242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17.5">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -13904,8 +14214,27 @@
       <c r="C17" s="64">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="43">
+        <v>0.84</v>
+      </c>
+      <c r="E17" s="43">
+        <v>0.76</v>
+      </c>
+      <c r="F17" s="43">
+        <v>1</v>
+      </c>
+      <c r="G17" s="65">
+        <v>42</v>
+      </c>
+      <c r="H17" s="64">
+        <v>73.138999999999996</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>0.86491557223262927</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17.5">
       <c r="A18" t="s">
         <v>154</v>
       </c>
@@ -13915,8 +14244,27 @@
       <c r="C18" s="64">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="43">
+        <v>0</v>
+      </c>
+      <c r="E18" s="43">
+        <v>0.77</v>
+      </c>
+      <c r="F18" s="43">
+        <v>0.92</v>
+      </c>
+      <c r="G18" s="64">
+        <v>27.3</v>
+      </c>
+      <c r="H18" s="64">
+        <v>99.132999999999996</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0.47490347490346546</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17.5">
       <c r="A19" t="s">
         <v>155</v>
       </c>
@@ -13926,8 +14274,18 @@
       <c r="C19" s="64">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="H19" s="64">
+        <v>270.68599999999998</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>0.48234581342233379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="17.5">
       <c r="A20" t="s">
         <v>156</v>
       </c>
@@ -13937,8 +14295,24 @@
       <c r="C20" s="64">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="43">
+        <v>0.54</v>
+      </c>
+      <c r="E20" s="43">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="43">
+        <v>0.87</v>
+      </c>
+      <c r="H20" s="64">
+        <v>116.208</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>0.1981447379743555</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17.5">
       <c r="A21" t="s">
         <v>157</v>
       </c>
@@ -13948,8 +14322,27 @@
       <c r="C21" s="64">
         <v>2.2825000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="43">
+        <v>0</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="64">
+        <v>78.114000000000004</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>9.9269789211257842E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17.5">
       <c r="A22" t="s">
         <v>158</v>
       </c>
@@ -13959,8 +14352,27 @@
       <c r="C22" s="64">
         <v>25.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="43">
+        <v>0</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="64">
+        <v>11.9</v>
+      </c>
+      <c r="H22" s="64">
+        <v>103.124</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>0.12558492110120734</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.5">
       <c r="A23" t="s">
         <v>159</v>
       </c>
@@ -13970,8 +14382,21 @@
       <c r="C23" s="64">
         <v>80.099999999999994</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23">
+        <v>18</v>
+      </c>
+      <c r="H23" s="64">
+        <v>18.015000000000001</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>0.31021194605012636</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17.5">
       <c r="A24" t="s">
         <v>159</v>
       </c>
@@ -13981,8 +14406,18 @@
       <c r="C24" s="64">
         <v>80.099999999999994</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="H24" s="64">
+        <v>18.015000000000001</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>0.48062015503874117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.5">
       <c r="A25" t="s">
         <v>160</v>
       </c>
@@ -13992,8 +14427,18 @@
       <c r="C25" s="64">
         <v>2.2799999999999998</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="H25" s="64">
+        <v>84.150999999999996</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>0.11741989951041605</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17.5">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -14003,8 +14448,24 @@
       <c r="C26" s="64">
         <v>6.44</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="43">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E26" s="43">
+        <v>0.45</v>
+      </c>
+      <c r="F26" s="43">
+        <v>1.03</v>
+      </c>
+      <c r="H26" s="63">
+        <v>278.34800000000001</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>0.15612536041366148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17.5">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -14014,8 +14475,18 @@
       <c r="C27" s="64">
         <v>2.27</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="H27" s="63">
+        <v>181.32300000000001</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>6.0120240480964197E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="17.5">
       <c r="A28" t="s">
         <v>161</v>
       </c>
@@ -14025,8 +14496,24 @@
       <c r="C28" s="64">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="43">
+        <v>0</v>
+      </c>
+      <c r="E28" s="43">
+        <v>0</v>
+      </c>
+      <c r="F28" s="43">
+        <v>0.54</v>
+      </c>
+      <c r="H28" s="63">
+        <v>136.238</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>0.11089331369912077</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="17.5">
       <c r="A29" t="s">
         <v>162</v>
       </c>
@@ -14036,8 +14523,27 @@
       <c r="C29" s="64">
         <v>6.06</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" s="43">
+        <v>0.17</v>
+      </c>
+      <c r="E29" s="43">
+        <v>0.47</v>
+      </c>
+      <c r="F29" s="43">
+        <v>0.82</v>
+      </c>
+      <c r="G29" s="65">
+        <v>33</v>
+      </c>
+      <c r="H29" s="64">
+        <v>107.15600000000001</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>0.15589353612171494</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="17.5">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -14047,8 +14553,24 @@
       <c r="C30" s="64">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" s="43">
+        <v>0.6</v>
+      </c>
+      <c r="E30" s="43">
+        <v>0.66</v>
+      </c>
+      <c r="F30" s="43">
+        <v>0.64</v>
+      </c>
+      <c r="H30" s="64">
+        <v>87.122</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>0.66366568735731257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17.5">
       <c r="A31" t="s">
         <v>163</v>
       </c>
@@ -14058,8 +14580,18 @@
       <c r="C31" s="64">
         <v>74.599999999999994</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="H31" s="64">
+        <v>34.014000000000003</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>0.13992249356281916</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17.5">
       <c r="A32" t="s">
         <v>164</v>
       </c>
@@ -14069,8 +14601,18 @@
       <c r="C32" s="64">
         <v>21.1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="H32" s="64">
+        <v>83.134</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>0.10734463276831212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.5">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -14080,8 +14622,27 @@
       <c r="C33" s="64">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="43">
+        <v>0</v>
+      </c>
+      <c r="E33" s="43">
+        <v>1.04</v>
+      </c>
+      <c r="F33" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="65">
+        <v>40</v>
+      </c>
+      <c r="H33" s="64">
+        <v>85.15</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>0.57142857142854098</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.5">
       <c r="A34" t="s">
         <v>165</v>
       </c>
@@ -14091,8 +14652,18 @@
       <c r="C34" s="64">
         <v>4.22</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="H34" s="63">
+        <v>80.09</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>7.875457875459041E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17.5">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -14102,8 +14673,27 @@
       <c r="C35" s="64">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="43">
+        <v>0.26</v>
+      </c>
+      <c r="E35" s="43">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F35" s="43">
+        <v>0.77</v>
+      </c>
+      <c r="G35">
+        <v>33.1</v>
+      </c>
+      <c r="H35" s="64">
+        <v>79.102000000000004</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>0.39131424174093205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17.5">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -14113,8 +14703,27 @@
       <c r="C36" s="64">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" s="43">
+        <v>0.26</v>
+      </c>
+      <c r="E36" s="43">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F36" s="43">
+        <v>0.77</v>
+      </c>
+      <c r="G36" s="65">
+        <v>33.1</v>
+      </c>
+      <c r="H36" s="64">
+        <v>79.102000000000004</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>0.5509160555377498</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.5">
       <c r="A37" t="s">
         <v>166</v>
       </c>
@@ -14124,8 +14733,18 @@
       <c r="C37" s="64">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="H37" s="64">
+        <v>84.132999999999996</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>0.31570123831670477</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17.5">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -14135,8 +14754,24 @@
       <c r="C38" s="64">
         <v>8.3000000000000007</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" s="43">
+        <v>0.16</v>
+      </c>
+      <c r="E38" s="43">
+        <v>0.7</v>
+      </c>
+      <c r="F38" s="43">
+        <v>0.39</v>
+      </c>
+      <c r="H38" s="64">
+        <v>71.123000000000005</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>0.86070778055449926</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17.5">
       <c r="A39" t="s">
         <v>167</v>
       </c>
@@ -14146,8 +14781,27 @@
       <c r="C39" s="64">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" s="43">
+        <v>0</v>
+      </c>
+      <c r="E39" s="43">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F39" s="43">
+        <v>1</v>
+      </c>
+      <c r="G39" s="65">
+        <v>20</v>
+      </c>
+      <c r="H39" s="64">
+        <v>72.106999999999999</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>0.34158884168696524</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17.5">
       <c r="A40" t="s">
         <v>168</v>
       </c>
@@ -14157,8 +14811,18 @@
       <c r="C40" s="64">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="H40" s="64">
+        <v>20.027000000000001</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>0.4153453225822602</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17.5">
       <c r="A41" t="s">
         <v>168</v>
       </c>
@@ -14168,8 +14832,18 @@
       <c r="C41" s="64">
         <v>78</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="H41" s="64">
+        <v>20.027000000000001</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>0.43193972200018216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17.5">
       <c r="A42" t="s">
         <v>159</v>
       </c>
@@ -14179,8 +14853,21 @@
       <c r="C42" s="64">
         <v>80.099999999999994</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42">
+        <v>18</v>
+      </c>
+      <c r="H42" s="64">
+        <v>18.015000000000001</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17.5">
       <c r="A43" t="s">
         <v>149</v>
       </c>
@@ -14190,8 +14877,27 @@
       <c r="C43" s="64">
         <v>38.799999999999997</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43" s="61">
+        <v>0.19</v>
+      </c>
+      <c r="E43" s="61">
+        <v>0.4</v>
+      </c>
+      <c r="F43" s="61">
+        <v>0.75</v>
+      </c>
+      <c r="G43" s="65">
+        <v>14.1</v>
+      </c>
+      <c r="H43" s="64">
+        <v>41.052999999999997</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="0"/>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="18" thickBot="1">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -14201,8 +14907,28 @@
       <c r="C44" s="64">
         <v>6.02</v>
       </c>
+      <c r="D44" s="51">
+        <v>0</v>
+      </c>
+      <c r="E44" s="51">
+        <v>0.45</v>
+      </c>
+      <c r="F44" s="51">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G44" s="65">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="H44" s="64">
+        <v>88.105999999999995</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="0"/>
+        <v>0.28809412324740097</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>